--- a/sources/metaPee/combined/subexposure_views/no/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/sources/metaPee/combined/subexposure_views/no/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -982,20 +982,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vitamin_b1</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1004,29 +1004,29 @@
       </c>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>2296</v>
+        <v>15914</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1142</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t>vitamin_b1</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2.92</v>
+        <v>2.53</v>
       </c>
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1035,29 +1035,29 @@
       </c>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>63257</v>
+        <v>2296</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>229</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>zinc</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.53</v>
+        <v>2.92</v>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1066,45 +1066,76 @@
       </c>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>2296</v>
+        <v>63257</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1142</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>13.84</v>
+        <v>2.53</v>
       </c>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
+        <v>2296</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
         <v>95958</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>353</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K20"/>
+  <autoFilter ref="A1:K21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
